--- a/public/template/training-attendance/crm/attendance-day1.xlsx
+++ b/public/template/training-attendance/crm/attendance-day1.xlsx
@@ -1,232 +1,308 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\培训 - 副本\CRM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CRM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>南货航飞行部培训签到表</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>CRM年度培训（第X期）</t>
+  </si>
+  <si>
+    <t>日期/地点</t>
+  </si>
+  <si>
+    <t>YYYY/MM/DD；广州从化壹泉湾温泉酒店</t>
+  </si>
+  <si>
+    <t>时长</t>
+  </si>
+  <si>
+    <t>09:00-17:00</t>
+  </si>
+  <si>
+    <t>培训教员</t>
+  </si>
+  <si>
+    <t>教员1、教员2</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>监控与自动化，惊吓与复原力</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>员工号</t>
+  </si>
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>签名</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="29">
     <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <sz val="12"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <sz val="18"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <name val="方正小标宋简体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="24"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="16"/>
-    </font>
-    <font>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <sz val="16"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="16"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <sz val="14"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -418,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -657,313 +733,269 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="15" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="15" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="17" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1">
-      <protection locked="0" hidden="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0">
+      <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1018,74 +1050,11 @@
     <cellStyle name="常规 10" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1374,228 +1343,470 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O56"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="35" customHeight="1"/>
   <cols>
-    <col width="16" customWidth="1" style="2" min="1" max="1"/>
-    <col width="23.75" customWidth="1" style="2" min="2" max="2"/>
-    <col width="24.875" customWidth="1" style="3" min="3" max="3"/>
-    <col width="29.1666666666667" customWidth="1" style="2" min="4" max="4"/>
-    <col width="27.7083333333333" customWidth="1" style="2" min="5" max="5"/>
-    <col width="9" customWidth="1" style="18" min="6" max="16383"/>
-    <col width="9" customWidth="1" style="4" min="16384" max="16384"/>
+    <col min="1" max="1" width="16" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="29.1666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.7083333333333" style="2" customWidth="1"/>
+    <col min="6" max="16383" width="9" style="1"/>
+    <col min="16384" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customFormat="1" customHeight="1" s="18">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>南货航飞行部培训签到表</t>
-        </is>
+    <row r="1" s="1" customFormat="1" ht="48" customHeight="1" spans="1:15">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="38" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="n"/>
-      <c r="C2" s="32" t="inlineStr">
-        <is>
-          <t>CRM年度培训（第X期）</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="n"/>
-      <c r="E2" s="33" t="n"/>
-    </row>
-    <row r="3" customFormat="1" s="18">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>日期/地点</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="n"/>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD；广州从化壹泉湾温泉酒店</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="33" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="18">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>时长</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="n"/>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>09:00-17:00</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="33" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="18">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>培训教员</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="n"/>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>教员1、教员2</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="33" t="n"/>
-    </row>
-    <row r="6" customFormat="1" s="18">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>监控与自动化，惊吓与复原力</t>
-        </is>
-      </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
-    </row>
-    <row r="7" ht="31" customFormat="1" customHeight="1" s="18">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="37" t="n"/>
-      <c r="D7" s="37" t="n"/>
-      <c r="E7" s="37" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="18" t="n"/>
-      <c r="O7" s="18" t="n"/>
-    </row>
-    <row r="8" customFormat="1" s="18">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>员工号</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>签名</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="18">
-      <c r="A9" s="20" t="n">
+      <c r="B1" s="5"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="38" customHeight="1" spans="1:15">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="23" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="18">
-      <c r="A10" s="20" t="n"/>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="23" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="18"/>
-    <row r="12" customFormat="1" s="18"/>
-    <row r="13" customFormat="1" s="18"/>
-    <row r="14" customFormat="1" s="18"/>
-    <row r="15" customFormat="1" s="18"/>
-    <row r="16" customFormat="1" s="18"/>
-    <row r="17" customFormat="1" s="18"/>
-    <row r="18" customFormat="1" s="18"/>
-    <row r="19" customFormat="1" s="18"/>
-    <row r="20" customFormat="1" s="18"/>
-    <row r="21" customFormat="1" s="18"/>
-    <row r="22" s="38"/>
-    <row r="23" s="38"/>
-    <row r="24" s="38"/>
-    <row r="25" s="38"/>
-    <row r="26" s="38"/>
-    <row r="27" s="38"/>
-    <row r="28" s="38"/>
-    <row r="29" s="38"/>
-    <row r="30" s="38"/>
-    <row r="31" s="38"/>
-    <row r="32" s="38"/>
-    <row r="33" s="38"/>
-    <row r="34" s="38"/>
-    <row r="35" s="38"/>
-    <row r="36" s="38"/>
-    <row r="37" ht="109" customHeight="1" s="38"/>
-    <row r="38" s="38"/>
-    <row r="39" s="38"/>
-    <row r="40" s="38"/>
-    <row r="41" s="38"/>
-    <row r="42" s="38"/>
-    <row r="43" s="38"/>
-    <row r="44" s="38"/>
-    <row r="45" s="38"/>
-    <row r="46" s="38"/>
-    <row r="47" s="38"/>
-    <row r="48" ht="64" customFormat="1" customHeight="1" s="18"/>
-    <row r="49" s="38"/>
-    <row r="50" s="38"/>
-    <row r="51" s="38"/>
-    <row r="52" s="38"/>
-    <row r="53" s="38"/>
-    <row r="54" s="38"/>
-    <row r="55" s="38"/>
-    <row r="56" s="38"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="31" customHeight="1" spans="1:15">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A9" s="20">
+        <v>1</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="23"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="23"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="23"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="23"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="23"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="23"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:5">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="26"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:5">
+      <c r="A23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="26"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:5">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="26"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:5">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="26"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:5">
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="26"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:5">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="26"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:5">
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="26"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:5">
+      <c r="A29" s="20"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="26"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:5">
+      <c r="A30" s="20"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="26"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:5">
+      <c r="A31" s="20"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="26"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:5">
+      <c r="A32" s="20"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="26"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:5">
+      <c r="A33" s="20"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="26"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:5">
+      <c r="A34" s="20"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="26"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:5">
+      <c r="A35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="26"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:5">
+      <c r="A36" s="20"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="26"/>
+    </row>
+    <row r="37" ht="109" customHeight="1" spans="1:5">
+      <c r="A37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="26"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:5">
+      <c r="A38" s="20"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="26"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:5">
+      <c r="A39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="26"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:5">
+      <c r="A40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="26"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:5">
+      <c r="A41" s="20"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="26"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:5">
+      <c r="A42" s="20"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="26"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:5">
+      <c r="A43" s="20"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="26"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:5">
+      <c r="A44" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="26"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:5">
+      <c r="A45" s="20"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="26"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:5">
+      <c r="A46" s="20"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="26"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:5">
+      <c r="A47" s="20"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="26"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="64" customHeight="1" spans="1:5">
+      <c r="A48" s="20"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="26"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:5">
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:5">
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:5">
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:5">
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:5">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:5">
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:5">
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:5">
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+    </row>
   </sheetData>
+  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C3:E3"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A3:B3"/>
     <mergeCell ref="B6:E7"/>
   </mergeCells>
   <pageMargins left="0.3125" right="0.196527777777778" top="0.865972222222222" bottom="0.472222222222222" header="0.141666666666667" footer="0.310416666666667"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="75" fitToHeight="0" horizontalDpi="600"/>
+  <pageSetup paperSize="9" scale="75" fitToHeight="0" orientation="portrait" horizontalDpi="600"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;R&amp;G</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
   </headerFooter>
+  <legacyDrawingHF r:id="rId1"/>
 </worksheet>
 </file>